--- a/datasets/WorkflowEngine_SR.xlsx
+++ b/datasets/WorkflowEngine_SR.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\Briefcase\Manuscripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B97750-EE1B-4833-9412-8350627C0116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874F19BC-A0CF-49F8-90FE-599B7B1C081B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Screening" sheetId="1" r:id="rId1"/>
+    <sheet name="Engines" sheetId="3" r:id="rId2"/>
+    <sheet name="Applications" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Screening!$A$1:$J$127</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="205">
   <si>
     <t xml:space="preserve">Title </t>
   </si>
@@ -436,9 +440,6 @@
   </si>
   <si>
     <t>PMID</t>
-  </si>
-  <si>
-    <t>B: Retracted</t>
   </si>
   <si>
     <t xml:space="preserve">N </t>
@@ -688,6 +689,9 @@
   </si>
   <si>
     <t>E: Description</t>
+  </si>
+  <si>
+    <t>B: Not Retracted</t>
   </si>
 </sst>
 </file>
@@ -799,7 +803,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -841,6 +845,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,22 +1229,22 @@
         <v>2</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>135</v>
-      </c>
       <c r="I1" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -1551,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>5</v>
@@ -4338,7 +4348,7 @@
         <v>4</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -4538,7 +4548,7 @@
         <v>10871211</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C105" s="4">
         <v>2000</v>
@@ -4547,22 +4557,22 @@
         <v>4</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
@@ -5178,7 +5188,7 @@
         <v>41385470</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C125" s="4">
         <v>2025</v>
@@ -5210,7 +5220,7 @@
         <v>41394085</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C126" s="4">
         <v>2025</v>
@@ -5242,7 +5252,7 @@
         <v>41450588</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" s="4">
         <v>2025</v>
@@ -5285,7 +5295,7 @@
       <c r="A129" s="13"/>
       <c r="B129" s="13"/>
       <c r="C129" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D129" s="13">
         <f>COUNTIF(D2:D128,"Y")</f>
@@ -5293,19 +5303,19 @@
       </c>
       <c r="E129" s="13">
         <f t="shared" ref="E129:J129" si="0">COUNTIF(E2:E128,"Y")</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F129" s="13">
         <f t="shared" si="0"/>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G129" s="13">
         <f t="shared" si="0"/>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H129" s="13">
         <f t="shared" ref="H129" si="1">COUNTIF(H2:H128,"Y")</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I129" s="13">
         <f>COUNTIF(I2:I128,"Y")</f>
@@ -5313,14 +5323,14 @@
       </c>
       <c r="J129" s="13">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="13"/>
       <c r="B130" s="13"/>
       <c r="C130" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D130" s="13">
         <f>COUNTIF(D2:D128,"N")</f>
@@ -5328,19 +5338,19 @@
       </c>
       <c r="E130" s="13">
         <f t="shared" ref="E130:J130" si="2">COUNTIF(E2:E128,"N")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F130" s="13">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G130" s="13">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H130" s="13">
         <f t="shared" ref="H130" si="3">COUNTIF(H2:H128,"N")</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I130" s="13">
         <f>COUNTIF(I2:I128,"=N")</f>
@@ -5348,14 +5358,14 @@
       </c>
       <c r="J130" s="13">
         <f t="shared" si="2"/>
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="13"/>
       <c r="B131" s="13"/>
       <c r="C131" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D131" s="13">
         <f>D129+D130</f>
@@ -5406,10 +5416,10 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="84.81640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="49.1796875" style="12" customWidth="1"/>
     <col min="3" max="3" width="6.81640625" style="12" customWidth="1"/>
     <col min="4" max="4" width="30.81640625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="28.36328125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" style="12" customWidth="1"/>
     <col min="6" max="6" width="18.1796875" style="12" customWidth="1"/>
     <col min="7" max="7" width="17.453125" style="12" customWidth="1"/>
     <col min="8" max="8" width="140.36328125" style="12" customWidth="1"/>
@@ -5427,19 +5437,19 @@
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>203</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5453,19 +5463,19 @@
         <v>2012</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5479,19 +5489,19 @@
         <v>2014</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -5505,19 +5515,19 @@
         <v>2023</v>
       </c>
       <c r="D4" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5531,19 +5541,19 @@
         <v>2016</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5557,19 +5567,19 @@
         <v>2005</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -5583,19 +5593,19 @@
         <v>2023</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5609,19 +5619,19 @@
         <v>2019</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5635,19 +5645,19 @@
         <v>2007</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5655,25 +5665,25 @@
         <v>37730936</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C10" s="3">
         <v>2023</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -5687,19 +5697,19 @@
         <v>2011</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -5713,19 +5723,19 @@
         <v>2017</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
@@ -5739,19 +5749,19 @@
         <v>2011</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -5765,19 +5775,19 @@
         <v>2017</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -5791,19 +5801,19 @@
         <v>2016</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -5817,19 +5827,19 @@
         <v>2008</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -5846,4 +5856,267 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12BBE696-CADC-4ECA-A308-8FEDB12D3B25}">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="73.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.81640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="80.1796875" style="19" customWidth="1"/>
+    <col min="3" max="16384" width="73.54296875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="16" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>34643507</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>38052452</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>38213704</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>37447786</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>35660516</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>30786165</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>35922700</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>33950394</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>31131402</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>40950129</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>34013039</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>25471934</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>32294771</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>23473722</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>24651862</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>30252445</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>25604327</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>40631125</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>37762547</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>23612443</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>28232853</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>19500956</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>17291828</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>28479932</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>21788681</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>20346188</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>16087095</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>16531352</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>27006915</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>41268369</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>